--- a/content/tz-ieroglif-semya.xlsx
+++ b/content/tz-ieroglif-semya.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -679,46 +679,58 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Целевой объём блока T123</t>
+          <t>Объём блока T123</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>40 000–45 000. Вилка подтвердилась: прошлая статья дала 41 409</t>
+          <t>ПЛАН 40 000–45 000. ФАКТ 41 673 — ВТОРОЕ ПОЛНОЕ ПОПАДАНИЕ ПОДРЯД</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция инфографики</t>
+          <t>Позиция инфографики</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>26–31 %</t>
+          <t>ПЛАН 26–31 %. ФАКТ 28,8 %</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция «Из личного опыта»</t>
+          <t>Позиция «Из личного опыта»</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>36–40 %</t>
+          <t>ПЛАН 36–40 %. ФАКТ 36,7 % (при первой сборке 40,1 %)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Позиция FAQ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>72,2 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Ключи и где отрабатываются</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>иероглиф семья на китайском — тайтл, H1, первый абзац, раздел 1, FAQ. семья иероглиф — раздел 1, паспорт знака, FAQ. семья на китайском языке иероглиф — разделы 4 и 5, FAQ</t>
         </is>
@@ -735,12 +747,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -778,7 +790,11 @@
           <t>40 000–45 000, лимит ≈ 50 000</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>41 673 — ВТОРОЕ ПОЛНОЕ ПОПАДАНИЕ ПОДРЯД. Вилка подтвердилась окончательно</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -791,7 +807,11 @@
           <t>26–31 %</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>28,8 %</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -804,7 +824,11 @@
           <t>36–40 %</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>36,7 %. При первой сборке 40,1 % — перенесена на абзац выше</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -817,7 +841,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>72,2 %</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -830,7 +858,11 @@
           <t>A = B</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>24 / 24</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -843,7 +875,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -856,7 +892,11 @@
           <t>position: sticky, top 90</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>sticky, top 90px</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -869,7 +909,11 @@
           <t>static, order 2, нет горизонтальной прокрутки</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>static, order 2, ширина документа 390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -882,7 +926,11 @@
           <t>да</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>да: BlogPosting, Person, EducationalOrganization, FAQPage, BreadcrumbList</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -895,7 +943,11 @@
           <t>совпадение полное</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>6 вопросов и 6 ответов, совпадение полное</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -908,7 +960,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0; ёлочек 38 пар</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -921,7 +977,11 @@
           <t>все верны</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>все семь верны</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -934,7 +994,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>одна найдена и исправлена: под крышей ЖИВЁТ свинья → СТОИТ</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -947,59 +1011,96 @@
           <t>все три</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>ПРОВЕРЕНО ПРОГРАММНО: одна из — 3 раза, версия/версий — 7, толкование — 5, предполагается и реконструкция — по разу, согласия нет — 1. КАТЕГОРИЧНЫХ УТВЕРЖДЕНИЙ О ПРОИСХОЖДЕНИИ: 0</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Правило .han в CSS</t>
+          <t>ПОЙМАНА СОБСТВЕННАЯ НЕТОЧНОСТЬ</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>есть, с запретом переноса</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr"/>
+          <t>в первом же абзаце</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Было: под крышей живёт свинья, ПОТОМУ ЧТО раньше скот в доме означал достаток. Читалось как утверждение, а статья ровно про то, что так говорить нельзя. Стало: под крышей стоит свинья, и это БУДТО БЫ память о временах, когда скот в доме означал достаток</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Высота инфографики</t>
+          <t>Правило .han в CSS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>подбирается замером</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
+          <t>есть, с запретом переноса</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>есть, унаследовано</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
+          <t>Высота инфографики</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>0 на отдаче</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr"/>
+          <t>подбирается замером</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>532 px при содержимом до 510, запас 22</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>Дефекты рендеров</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>0 на отдаче</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>НЕ НАЙДЕНО. Обе картинки чистые с первого раза</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Адреса Tilda вшиты</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>7 в исходнике / 5 в блоке, assets = 0</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>ждём ссылки от заказчика</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1862,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2002,10 +2103,31 @@
           <t>Дефекты рендеров</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>НЕ НАЙДЕНО</t>
+        </is>
+      </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>проставляется после просмотра</t>
+          <t>Обе картинки вышли чистыми с первого раза: наложений, обрезанного текста и пустых полос нет. На обложке подсветка легла ровно по границе графем — крыша 宀 вне зоны, 豕 внутри</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Единственная правка</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>высота холста инфографики</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>содержимое оказалось на 60 px выше заявленного: 532 px при содержимом до 510</t>
         </is>
       </c>
     </row>

--- a/content/tz-ieroglif-semya.xlsx
+++ b/content/tz-ieroglif-semya.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ПЛАН 40 000–45 000. ФАКТ 41 673 — ВТОРОЕ ПОЛНОЕ ПОПАДАНИЕ ПОДРЯД</t>
+          <t>ПЛАН 40 000–45 000. ФАКТ 41 890 с адресами Tilda — ВТОРОЕ ПОЛНОЕ ПОПАДАНИЕ ПОДРЯД</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>41 673 — ВТОРОЕ ПОЛНОЕ ПОПАДАНИЕ ПОДРЯД. Вилка подтвердилась окончательно</t>
+          <t>41 890 с адресами Tilda — ВТОРОЕ ПОЛНОЕ ПОПАДАНИЕ ПОДРЯД. Вилка подтвердилась окончательно</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ждём ссылки от заказчика</t>
+          <t>7 / 5, assets = 0. ПОРЯДОК ПРОВЕРЕН ПО ИМЕНАМ: слаг короткий, обрезка Tilda различие не съела — ieroglif-semya.png обложка, ieroglif-semya-versi.png инфографика. Проблема возникает только у длинных слагов; предложение про oblozhka- и infografika- остаётся в силе</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com — подставляется после загрузки</t>
+          <t>https://static.tildacdn.com/tild6530-6663-4232-b234-313563306632/ieroglif-semya.png</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com</t>
+          <t>https://static.tildacdn.com/tild6530-6663-4232-b234-313563306632/ieroglif-semya.png</t>
         </is>
       </c>
     </row>
